--- a/laporan_padel_dki_jakarta_2026-10-17.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-17.xlsx
@@ -713,7 +713,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp250.000</t>
+          <t>Rp99.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp18.740.000</t>
+          <t>Rp19.015.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.950.000</t>
+          <t>Rp3.100.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp125.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>18</v>
       </c>
       <c r="D55" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp1.043.000</t>
+          <t>Rp1.192.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp2.290.000</t>
+          <t>Rp3.650.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Rp80.000 - Rp180.000</t>
+          <t>Rp80.000 - Rp125.000</t>
         </is>
       </c>
     </row>
@@ -3974,16 +3974,16 @@
         <v>48</v>
       </c>
       <c r="D15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.760.000</t>
+          <t>Rp2.880.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp5.000.000</t>
+          <t>Rp5.200.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4687,16 +4687,16 @@
         <v>45</v>
       </c>
       <c r="D38" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4811,16 +4811,16 @@
         <v>48</v>
       </c>
       <c r="D42" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp5.900.000</t>
+          <t>Rp5.150.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp513.000</t>
+          <t>Rp586.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5338,16 +5338,16 @@
         <v>124</v>
       </c>
       <c r="D59" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp760.000</t>
+          <t>Rp960.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>64</v>
       </c>
       <c r="D63" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp7.000.000</t>
+          <t>Rp7.500.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp7.100.000</t>
+          <t>Rp7.350.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6319,16 +6319,16 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp4.675.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.350.000</t>
+          <t>Rp5.525.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.291.000</t>
+          <t>Rp1.142.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>108</v>
       </c>
       <c r="D26" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp4.420.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.625.000</t>
+          <t>Rp3.125.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp19.400.000</t>
+          <t>Rp19.500.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>112</v>
       </c>
       <c r="D45" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp11.625.000</t>
+          <t>Rp11.400.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -8013,16 +8013,16 @@
         <v>102</v>
       </c>
       <c r="D51" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp5.850.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp15.830.000</t>
+          <t>Rp16.090.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp13.325.000</t>
+          <t>Rp13.610.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>36</v>
       </c>
       <c r="D24" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp175.000</t>
+          <t>Rp350.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp2.975.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>34</v>
       </c>
       <c r="D33" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.190.000</t>
+          <t>Rp2.780.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>36</v>
       </c>
       <c r="D34" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.515.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9242,16 +9242,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp4.995.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>54</v>
       </c>
       <c r="D38" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp3.850.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>64</v>
       </c>
       <c r="D39" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.535.000</t>
+          <t>Rp2.704.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9366,16 +9366,16 @@
         <v>68</v>
       </c>
       <c r="D41" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.160.000</t>
+          <t>Rp2.340.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-17.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-17.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.820.000</t>
+          <t>Rp1.890.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -544,16 +544,16 @@
         <v>144</v>
       </c>
       <c r="D4" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp19.000.000</t>
+          <t>Rp19.500.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp5.400.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -699,16 +699,16 @@
         <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.950.000</t>
+          <t>Rp3.100.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.348.000</t>
+          <t>Rp5.517.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -761,16 +761,16 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp4.925.000</t>
+          <t>Rp4.575.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.378.000</t>
+          <t>Rp3.080.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp19.015.000</t>
+          <t>Rp18.428.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.225.000</t>
+          <t>Rp3.575.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp1.920.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.390.000</t>
+          <t>Rp1.540.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp625.000</t>
+          <t>Rp875.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp5.012.000</t>
+          <t>Rp4.654.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>68</v>
       </c>
       <c r="D40" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.925.000</t>
+          <t>Rp3.105.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp9.553.000</t>
+          <t>Rp9.753.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>30</v>
       </c>
       <c r="D52" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp1.900.000</t>
+          <t>Rp2.050.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp2.925.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>36</v>
       </c>
       <c r="D59" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp99.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>72</v>
       </c>
       <c r="D62" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp1.378.000</t>
+          <t>Rp1.726.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp309.000</t>
+          <t>Rp280.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>128</v>
       </c>
       <c r="D69" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp3.184.000</t>
+          <t>Rp3.980.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>108</v>
       </c>
       <c r="D70" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp6.630.000</t>
+          <t>Rp7.420.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>68</v>
       </c>
       <c r="D71" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp1.020.000</t>
+          <t>Rp1.140.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>98</v>
       </c>
       <c r="D75" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp3.240.000</t>
+          <t>Rp4.110.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>45</v>
       </c>
       <c r="D76" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp2.970.000</t>
+          <t>Rp3.168.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp3.650.000</t>
+          <t>Rp3.850.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>112</v>
       </c>
       <c r="D96" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp7.650.000</t>
+          <t>Rp7.850.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.782.000</t>
+          <t>Rp1.863.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>126</v>
       </c>
       <c r="D3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp19.271.000</t>
+          <t>Rp19.453.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp3.070.000</t>
+          <t>Rp3.430.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.400.000</t>
+          <t>Rp3.500.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp6.625.000</t>
+          <t>Rp7.005.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.796.000</t>
+          <t>Rp4.596.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp9.850.000</t>
+          <t>Rp11.950.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.430.000</t>
+          <t>Rp1.820.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4253,16 +4253,16 @@
         <v>53</v>
       </c>
       <c r="D24" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp16.600.000</t>
+          <t>Rp16.250.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>64</v>
       </c>
       <c r="D27" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp5.500.000</t>
+          <t>Rp6.050.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4408,16 +4408,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.450.000</t>
+          <t>Rp3.975.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4687,16 +4687,16 @@
         <v>45</v>
       </c>
       <c r="D38" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>32</v>
       </c>
       <c r="D48" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>90</v>
       </c>
       <c r="D50" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp7.200.000</t>
+          <t>Rp7.650.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>54</v>
       </c>
       <c r="D52" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp7.000.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>68</v>
       </c>
       <c r="D55" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp6.820.000</t>
+          <t>Rp6.270.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp586.000</t>
+          <t>Rp928.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>51</v>
       </c>
       <c r="D58" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp700.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5338,16 +5338,16 @@
         <v>124</v>
       </c>
       <c r="D59" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp960.000</t>
+          <t>Rp1.360.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>64</v>
       </c>
       <c r="D63" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp7.500.000</t>
+          <t>Rp8.500.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp12.304.000</t>
+          <t>Rp12.482.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp7.350.000</t>
+          <t>Rp7.100.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>34</v>
       </c>
       <c r="D70" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>82.4%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp4.775.000</t>
+          <t>Rp5.125.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5772,16 +5772,16 @@
         <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp14.750.000</t>
+          <t>Rp16.150.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp13.475.000</t>
+          <t>Rp13.860.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp4.750.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.280.000</t>
+          <t>Rp1.360.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.250.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.260.000</t>
+          <t>Rp1.440.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.575.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp13.590.000</t>
+          <t>Rp13.860.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp198.000</t>
+          <t>Rp596.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp17.130.000</t>
+          <t>Rp17.310.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>90</v>
       </c>
       <c r="D9" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp8.500.000</t>
+          <t>Rp8.750.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp700.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.196.000</t>
+          <t>Rp3.572.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.525.000</t>
+          <t>Rp6.050.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.097.000</t>
+          <t>Rp3.497.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>36</v>
       </c>
       <c r="D27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.440.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>68</v>
       </c>
       <c r="D29" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp3.850.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp5.116.000</t>
+          <t>Rp5.501.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp19.500.000</t>
+          <t>Rp19.900.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>108</v>
       </c>
       <c r="D37" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp1.639.000</t>
+          <t>Rp2.533.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>180</v>
       </c>
       <c r="D38" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp3.350.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>34</v>
       </c>
       <c r="D39" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp288.000</t>
+          <t>Rp664.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>170</v>
       </c>
       <c r="D41" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp21.410.000</t>
+          <t>Rp22.008.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>112</v>
       </c>
       <c r="D45" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp11.400.000</t>
+          <t>Rp11.625.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>102</v>
       </c>
       <c r="D47" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7982,16 +7982,16 @@
         <v>102</v>
       </c>
       <c r="D50" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp4.257.000</t>
+          <t>Rp4.515.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8044,16 +8044,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp16.090.000</t>
+          <t>Rp16.780.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp4.250.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>51</v>
       </c>
       <c r="D7" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.625.000</t>
+          <t>Rp3.395.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>108</v>
       </c>
       <c r="D10" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.590.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>48</v>
       </c>
       <c r="D13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp6.250.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>68</v>
       </c>
       <c r="D22" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp2.475.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.720.000</t>
+          <t>Rp6.930.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>36</v>
       </c>
       <c r="D24" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp350.000</t>
+          <t>Rp650.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D25" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.599.982</t>
+          <t>Rp4.199.979</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>32</v>
       </c>
       <c r="D28" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>45</v>
       </c>
       <c r="D29" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp2.025.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.185.000</t>
+          <t>Rp3.675.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>36</v>
       </c>
       <c r="D34" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp4.790.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>51</v>
       </c>
       <c r="D36" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.295.000</t>
+          <t>Rp1.665.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>54</v>
       </c>
       <c r="D38" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.850.000</t>
+          <t>Rp4.050.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9366,16 +9366,16 @@
         <v>68</v>
       </c>
       <c r="D41" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.340.000</t>
+          <t>Rp3.060.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -9397,16 +9397,16 @@
         <v>64</v>
       </c>
       <c r="D42" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp6.500.000</t>
+          <t>Rp6.670.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-17.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-17.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.890.000</t>
+          <t>Rp1.960.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp3.564.000</t>
+          <t>Rp3.663.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp616.000</t>
+          <t>Rp968.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.517.000</t>
+          <t>Rp5.067.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.080.000</t>
+          <t>Rp3.378.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp18.428.000</t>
+          <t>Rp18.895.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp1.920.000</t>
+          <t>Rp4.590.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>136</v>
       </c>
       <c r="D21" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp14.945.000</t>
+          <t>Rp15.320.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.100.000</t>
+          <t>Rp4.300.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.540.000</t>
+          <t>Rp1.840.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp5.031.000</t>
+          <t>Rp5.547.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp7.200.000</t>
+          <t>Rp7.680.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.150.000</t>
+          <t>Rp5.530.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.654.000</t>
+          <t>Rp5.728.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp3.156.000</t>
+          <t>Rp4.134.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp9.753.000</t>
+          <t>Rp9.853.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp125.000</t>
+          <t>Rp275.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>45</v>
       </c>
       <c r="D46" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp850.000</t>
+          <t>Rp1.700.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp1.660.000</t>
+          <t>Rp1.760.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>105</v>
       </c>
       <c r="D48" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp5.060.000</t>
+          <t>Rp6.340.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>48</v>
       </c>
       <c r="D56" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp1.890.000</t>
+          <t>Rp1.690.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp3.375.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>41</v>
       </c>
       <c r="D67" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp190.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp1.805.000</t>
+          <t>Rp1.275.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp9.275.000</t>
+          <t>Rp8.625.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>98</v>
       </c>
       <c r="D75" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp4.110.000</t>
+          <t>Rp4.490.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>120</v>
       </c>
       <c r="D77" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp6.020.000</t>
+          <t>Rp4.795.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.175.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp3.168.000</t>
+          <t>Rp3.664.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>54</v>
       </c>
       <c r="D81" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp1.683.000</t>
+          <t>Rp1.881.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -2962,16 +2962,16 @@
         <v>36</v>
       </c>
       <c r="D82" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>80</v>
       </c>
       <c r="D87" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp796.000</t>
+          <t>Rp996.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp3.850.000</t>
+          <t>Rp3.280.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>119</v>
       </c>
       <c r="D90" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp5.125.000</t>
+          <t>Rp5.830.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3334,16 +3334,16 @@
         <v>34</v>
       </c>
       <c r="D94" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp1.125.000</t>
+          <t>Rp1.375.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>112</v>
       </c>
       <c r="D96" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp7.850.000</t>
+          <t>Rp8.790.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>68</v>
       </c>
       <c r="D98" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp945.000</t>
+          <t>Rp1.095.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp3.890.000</t>
+          <t>Rp6.224.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp7.005.000</t>
+          <t>Rp7.795.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>40</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.425.000</t>
+          <t>Rp1.735.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>65</v>
       </c>
       <c r="D17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp11.565.000</t>
+          <t>Rp11.970.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp5.200.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.125.000</t>
+          <t>Rp1.375.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp3.375.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.820.000</t>
+          <t>Rp2.080.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>54</v>
       </c>
       <c r="D25" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp3.970.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>64</v>
       </c>
       <c r="D27" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp6.050.000</t>
+          <t>Rp6.875.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.975.000</t>
+          <t>Rp4.875.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4687,16 +4687,16 @@
         <v>45</v>
       </c>
       <c r="D38" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp7.125.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4718,16 +4718,16 @@
         <v>24</v>
       </c>
       <c r="D39" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.400.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>90</v>
       </c>
       <c r="D50" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp7.650.000</t>
+          <t>Rp7.875.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>72</v>
       </c>
       <c r="D51" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp3.980.000</t>
+          <t>Rp5.970.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp3.400.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>112</v>
       </c>
       <c r="D56" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp928.000</t>
+          <t>Rp1.334.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>32</v>
       </c>
       <c r="D60" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp940.000</t>
+          <t>Rp1.175.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5400,16 +5400,16 @@
         <v>45</v>
       </c>
       <c r="D61" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp4.750.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>64</v>
       </c>
       <c r="D63" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp8.500.000</t>
+          <t>Rp11.000.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp5.400.000</t>
+          <t>Rp6.300.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp12.482.000</t>
+          <t>Rp12.592.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5617,16 +5617,16 @@
         <v>72</v>
       </c>
       <c r="D68" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp11.080.000</t>
+          <t>Rp12.480.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5741,16 +5741,16 @@
         <v>162</v>
       </c>
       <c r="D72" t="n">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp4.350.000</t>
+          <t>Rp7.000.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5772,16 +5772,16 @@
         <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp16.150.000</t>
+          <t>Rp15.800.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.125.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp1.250.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp3.825.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.800.000</t>
+          <t>Rp4.180.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6381,16 +6381,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp752.000</t>
+          <t>Rp940.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6412,16 +6412,16 @@
         <v>64</v>
       </c>
       <c r="D20" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.596.000</t>
+          <t>Rp3.192.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp13.860.000</t>
+          <t>Rp14.160.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp596.000</t>
+          <t>Rp803.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>90</v>
       </c>
       <c r="D9" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp8.750.000</t>
+          <t>Rp9.375.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp17.520.000</t>
+          <t>Rp17.860.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.300.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.572.000</t>
+          <t>Rp4.324.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp7.525.000</t>
+          <t>Rp8.325.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp6.050.000</t>
+          <t>Rp6.625.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.450.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.142.000</t>
+          <t>Rp1.589.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp17.850.000</t>
+          <t>Rp18.850.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp7.000.000</t>
+          <t>Rp5.200.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>90</v>
       </c>
       <c r="D24" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.400.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>108</v>
       </c>
       <c r="D26" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.420.000</t>
+          <t>Rp4.760.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>36</v>
       </c>
       <c r="D27" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp1.440.000</t>
+          <t>Rp1.620.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>96</v>
       </c>
       <c r="D28" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp2.300.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>68</v>
       </c>
       <c r="D29" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.550.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp5.501.000</t>
+          <t>Rp5.982.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.125.000</t>
+          <t>Rp2.125.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp19.900.000</t>
+          <t>Rp20.900.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>108</v>
       </c>
       <c r="D37" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp2.533.000</t>
+          <t>Rp2.831.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>180</v>
       </c>
       <c r="D38" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.350.000</t>
+          <t>Rp3.625.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>170</v>
       </c>
       <c r="D41" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp22.008.000</t>
+          <t>Rp23.255.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>112</v>
       </c>
       <c r="D45" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp11.625.000</t>
+          <t>Rp11.400.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>174</v>
       </c>
       <c r="D46" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp40.200.000</t>
+          <t>Rp41.200.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>102</v>
       </c>
       <c r="D47" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp3.850.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7920,16 +7920,16 @@
         <v>36</v>
       </c>
       <c r="D48" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp7.350.000</t>
+          <t>Rp7.850.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7951,16 +7951,16 @@
         <v>108</v>
       </c>
       <c r="D49" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7982,16 +7982,16 @@
         <v>102</v>
       </c>
       <c r="D50" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp4.515.000</t>
+          <t>Rp4.773.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8044,16 +8044,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.300.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8075,16 +8075,16 @@
         <v>90</v>
       </c>
       <c r="D53" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp5.800.000</t>
+          <t>Rp6.200.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp16.780.000</t>
+          <t>Rp18.760.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>51</v>
       </c>
       <c r="D7" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp3.395.000</t>
+          <t>Rp3.945.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp13.610.000</t>
+          <t>Rp13.890.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>48</v>
       </c>
       <c r="D13" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp6.500.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.599.972</t>
+          <t>Rp5.799.971</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp3.375.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.930.000</t>
+          <t>Rp7.980.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>45</v>
       </c>
       <c r="D29" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.675.000</t>
+          <t>Rp4.165.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>36</v>
       </c>
       <c r="D34" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp4.790.000</t>
+          <t>Rp5.615.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>120</v>
       </c>
       <c r="D35" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp5.460.000</t>
+          <t>Rp6.290.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>51</v>
       </c>
       <c r="D36" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.665.000</t>
+          <t>Rp2.035.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9242,16 +9242,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.400.000</t>
+          <t>Rp5.535.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>54</v>
       </c>
       <c r="D38" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp4.300.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>64</v>
       </c>
       <c r="D39" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.704.000</t>
+          <t>Rp2.873.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9366,16 +9366,16 @@
         <v>68</v>
       </c>
       <c r="D41" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp3.060.000</t>
+          <t>Rp4.140.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-17.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-17.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.960.000</t>
+          <t>Rp2.030.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp968.000</t>
+          <t>Rp1.144.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -699,16 +699,16 @@
         <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.100.000</t>
+          <t>Rp3.298.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.590.000</t>
+          <t>Rp4.910.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.494.000</t>
+          <t>Rp1.992.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>136</v>
       </c>
       <c r="D21" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp15.320.000</t>
+          <t>Rp14.710.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp8.700.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp4.300.000</t>
+          <t>Rp4.450.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.840.000</t>
+          <t>Rp2.140.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp5.728.000</t>
+          <t>Rp5.907.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp4.134.000</t>
+          <t>Rp3.354.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>60</v>
       </c>
       <c r="D45" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp2.520.000</t>
+          <t>Rp1.260.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp560.000</t>
+          <t>Rp705.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>48</v>
       </c>
       <c r="D56" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp1.690.000</t>
+          <t>Rp1.090.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>36</v>
       </c>
       <c r="D59" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp99.000</t>
+          <t>Rp397.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>72</v>
       </c>
       <c r="D62" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp1.726.000</t>
+          <t>Rp2.116.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>41</v>
       </c>
       <c r="D67" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp190.000</t>
+          <t>Rp400.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>34</v>
       </c>
       <c r="D68" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp1.485.000</t>
+          <t>Rp1.683.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>108</v>
       </c>
       <c r="D70" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp7.420.000</t>
+          <t>Rp7.720.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.350.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp3.664.000</t>
+          <t>Rp4.258.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>108</v>
       </c>
       <c r="D85" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp6.600.000</t>
+          <t>Rp5.700.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>36</v>
       </c>
       <c r="D86" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp3.280.000</t>
+          <t>Rp3.730.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3272,16 +3272,16 @@
         <v>28</v>
       </c>
       <c r="D92" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rp1.094.000</t>
+          <t>Rp594.000</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3489,16 +3489,16 @@
         <v>32</v>
       </c>
       <c r="D99" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rp200.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp6.050.000</t>
+          <t>Rp6.400.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>65</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp11.970.000</t>
+          <t>Rp12.780.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp5.800.000</t>
+          <t>Rp6.400.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>176</v>
       </c>
       <c r="D37" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp25.850.000</t>
+          <t>Rp26.000.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp1.334.000</t>
+          <t>Rp1.432.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>51</v>
       </c>
       <c r="D58" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5400,16 +5400,16 @@
         <v>45</v>
       </c>
       <c r="D61" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp4.750.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>102</v>
       </c>
       <c r="D66" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp1.980.000</t>
+          <t>Rp2.520.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5741,16 +5741,16 @@
         <v>162</v>
       </c>
       <c r="D72" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp7.000.000</t>
+          <t>Rp7.350.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp2.148.000</t>
+          <t>Rp2.546.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp14.160.000</t>
+          <t>Rp14.250.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp5.950.000</t>
+          <t>Rp6.750.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp8.325.000</t>
+          <t>Rp7.925.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.497.000</t>
+          <t>Rp4.743.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp18.850.000</t>
+          <t>Rp19.250.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7145,21 +7145,21 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.885.000</t>
+          <t>Rp6.895.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rp81.000</t>
+          <t>Rp10.000 - Rp81.000</t>
         </is>
       </c>
     </row>
@@ -7176,16 +7176,16 @@
         <v>90</v>
       </c>
       <c r="D24" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp6.150.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>108</v>
       </c>
       <c r="D26" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.760.000</t>
+          <t>Rp5.100.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp5.982.000</t>
+          <t>Rp6.059.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp20.900.000</t>
+          <t>Rp21.250.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.512.000</t>
+          <t>Rp3.948.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>108</v>
       </c>
       <c r="D37" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp2.831.000</t>
+          <t>Rp2.235.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>180</v>
       </c>
       <c r="D38" t="n">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.625.000</t>
+          <t>Rp3.825.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>112</v>
       </c>
       <c r="D45" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp11.400.000</t>
+          <t>Rp11.850.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7982,16 +7982,16 @@
         <v>102</v>
       </c>
       <c r="D50" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp4.773.000</t>
+          <t>Rp4.902.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8044,16 +8044,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp2.300.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>70</v>
       </c>
       <c r="D6" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp598.000</t>
+          <t>Rp2.392.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>51</v>
       </c>
       <c r="D7" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp3.945.000</t>
+          <t>Rp4.770.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp13.890.000</t>
+          <t>Rp14.170.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>48</v>
       </c>
       <c r="D13" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp6.500.000</t>
+          <t>Rp7.000.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.799.971</t>
+          <t>Rp5.999.970</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp20.040.000</t>
+          <t>Rp20.840.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>68</v>
       </c>
       <c r="D22" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp3.375.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.980.000</t>
+          <t>Rp8.400.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp5.100.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp3.050.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>34</v>
       </c>
       <c r="D33" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.780.000</t>
+          <t>Rp3.325.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>120</v>
       </c>
       <c r="D35" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp6.290.000</t>
+          <t>Rp6.490.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>51</v>
       </c>
       <c r="D36" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.035.000</t>
+          <t>Rp2.220.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>54</v>
       </c>
       <c r="D38" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.300.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>64</v>
       </c>
       <c r="D39" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.873.000</t>
+          <t>Rp3.211.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9366,16 +9366,16 @@
         <v>68</v>
       </c>
       <c r="D41" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp4.140.000</t>
+          <t>Rp3.780.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -9397,16 +9397,16 @@
         <v>64</v>
       </c>
       <c r="D42" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp6.670.000</t>
+          <t>Rp7.330.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-17.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-17.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp2.030.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.144.000</t>
+          <t>Rp1.320.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp24.560.000</t>
+          <t>Rp25.060.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp18.895.500</t>
+          <t>Rp19.363.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>136</v>
       </c>
       <c r="D21" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp14.710.000</t>
+          <t>Rp15.015.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp8.700.000</t>
+          <t>Rp9.000.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp4.450.000</t>
+          <t>Rp4.600.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>64</v>
       </c>
       <c r="D32" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.261.000</t>
+          <t>Rp2.381.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp5.547.000</t>
+          <t>Rp5.805.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.900.000</t>
+          <t>Rp4.050.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>68</v>
       </c>
       <c r="D40" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp3.354.000</t>
+          <t>Rp4.719.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp275.000</t>
+          <t>Rp425.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>36</v>
       </c>
       <c r="D59" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp397.000</t>
+          <t>Rp893.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>41</v>
       </c>
       <c r="D67" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp330.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>128</v>
       </c>
       <c r="D69" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp3.980.000</t>
+          <t>Rp3.781.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>108</v>
       </c>
       <c r="D70" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp7.720.000</t>
+          <t>Rp7.870.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>120</v>
       </c>
       <c r="D77" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp4.795.000</t>
+          <t>Rp4.550.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>54</v>
       </c>
       <c r="D81" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp1.881.000</t>
+          <t>Rp1.980.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>119</v>
       </c>
       <c r="D90" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp5.830.000</t>
+          <t>Rp5.955.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp8.790.000</t>
+          <t>Rp9.030.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp950.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp955.000</t>
+          <t>Rp1.205.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>176</v>
       </c>
       <c r="D37" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp26.000.000</t>
+          <t>Rp26.650.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>90</v>
       </c>
       <c r="D50" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp7.875.000</t>
+          <t>Rp8.000.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>54</v>
       </c>
       <c r="D52" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp7.000.000</t>
+          <t>Rp7.250.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp1.432.000</t>
+          <t>Rp1.505.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5400,16 +5400,16 @@
         <v>45</v>
       </c>
       <c r="D61" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp5.000.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp13.860.000</t>
+          <t>Rp13.475.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.750.000</t>
+          <t>Rp5.850.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp14.250.000</t>
+          <t>Rp15.200.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp803.000</t>
+          <t>Rp1.139.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp19.250.000</t>
+          <t>Rp19.650.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.895.000</t>
+          <t>Rp7.067.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp21.250.000</t>
+          <t>Rp21.725.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>108</v>
       </c>
       <c r="D37" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp2.235.000</t>
+          <t>Rp2.533.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>80</v>
       </c>
       <c r="D43" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp2.125.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp18.760.000</t>
+          <t>Rp19.260.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp450.000</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp14.170.000</t>
+          <t>Rp13.970.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>36</v>
       </c>
       <c r="D34" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp5.615.000</t>
+          <t>Rp5.810.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
